--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.74199254134886</v>
+        <v>14.09557378796919</v>
       </c>
       <c r="D2" t="n">
-        <v>85.70963911256889</v>
+        <v>13.92781635579245</v>
       </c>
       <c r="E2" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F2" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0799722119523</v>
+        <v>3.912995484442249</v>
       </c>
       <c r="D3" t="n">
-        <v>29.59694453484179</v>
+        <v>4.80950348691179</v>
       </c>
       <c r="E3" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F3" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.73047269533988</v>
+        <v>10.51870181299273</v>
       </c>
       <c r="D4" t="n">
-        <v>63.10763684334891</v>
+        <v>10.2549909870442</v>
       </c>
       <c r="E4" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F4" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.35642408025188</v>
+        <v>12.40791891304093</v>
       </c>
       <c r="D5" t="n">
-        <v>74.77081041668384</v>
+        <v>12.15025669271112</v>
       </c>
       <c r="E5" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F5" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>90.21059345818961</v>
+        <v>14.65922143695581</v>
       </c>
       <c r="D6" t="n">
-        <v>88.798728043069</v>
+        <v>14.42979330699871</v>
       </c>
       <c r="E6" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F6" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.1605930076129</v>
+        <v>10.9135963637371</v>
       </c>
       <c r="D7" t="n">
-        <v>69.01412222046605</v>
+        <v>11.21479486082573</v>
       </c>
       <c r="E7" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F7" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.1283498043485</v>
+        <v>8.95835684320663</v>
       </c>
       <c r="D8" t="n">
-        <v>56.94963502174303</v>
+        <v>9.254315691033243</v>
       </c>
       <c r="E8" t="n">
-        <v>20.70627981913657</v>
+        <v>3.364770470609692</v>
       </c>
       <c r="F8" t="n">
-        <v>18.53440030289195</v>
+        <v>3.011840049219941</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
